--- a/Data_Kriging.xlsx
+++ b/Data_Kriging.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E71D107-4D34-4B53-904F-CBE0D713450F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7DB929-E90B-4B71-9D62-A0705B9CD76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{BD3995A2-FA7A-463B-B94C-CD56ACD34186}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>Desa</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>Bakal</t>
+  </si>
+  <si>
+    <t>Elevasi</t>
+  </si>
+  <si>
+    <t>Kecocokan</t>
+  </si>
+  <si>
+    <t>Cocok</t>
   </si>
 </sst>
 </file>
@@ -121,7 +130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -218,11 +227,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -230,41 +265,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -602,62 +652,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A8F9D5-CB17-4C42-BBD2-890CE6F3D0E8}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="H1" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="17">
         <v>-7.1903236000000001</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="17">
         <v>109.8794669</v>
       </c>
       <c r="D4" s="2">
@@ -669,14 +731,20 @@
       <c r="F4" s="2">
         <v>5</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="H4" s="18">
+        <v>1895</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="2">
         <v>4</v>
       </c>
@@ -686,14 +754,16 @@
       <c r="F5" s="2">
         <v>14</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="2">
         <v>3</v>
       </c>
@@ -703,14 +773,16 @@
       <c r="F6" s="2">
         <v>12</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
       <c r="D7" s="2">
         <v>3</v>
       </c>
@@ -720,18 +792,20 @@
       <c r="F7" s="2">
         <v>12</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="7">
         <v>-7.2237650000000002</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="7">
         <v>109.8706483</v>
       </c>
       <c r="D8" s="1">
@@ -743,14 +817,20 @@
       <c r="F8" s="1">
         <v>16</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="4">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="H8" s="18">
+        <v>1823</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="1">
         <v>5</v>
       </c>
@@ -760,18 +840,20 @@
       <c r="F9" s="1">
         <v>18</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="4">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="7">
         <v>-7.2279198999999998</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="7">
         <v>109.9022739</v>
       </c>
       <c r="D10" s="1">
@@ -783,11 +865,17 @@
       <c r="F10" s="1">
         <v>2</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="4">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="18">
+        <v>2074</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -800,11 +888,13 @@
       <c r="F11" s="1">
         <v>11</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="4">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -817,14 +907,16 @@
       <c r="F12" s="1">
         <v>13</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="4">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
       <c r="D13" s="1">
         <v>3</v>
       </c>
@@ -834,18 +926,20 @@
       <c r="F13" s="1">
         <v>10</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="4">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="7">
         <v>-7.2018072999999996</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="7">
         <v>109.91100179999999</v>
       </c>
       <c r="D14" s="2">
@@ -857,11 +951,17 @@
       <c r="F14" s="2">
         <v>17</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="3">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="18">
+        <v>2077</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -874,11 +974,13 @@
       <c r="F15" s="2">
         <v>24</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -891,14 +993,16 @@
       <c r="F16" s="2">
         <v>30</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="3">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
       <c r="D17" s="2">
         <v>6</v>
       </c>
@@ -908,18 +1012,20 @@
       <c r="F17" s="2">
         <v>20</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="3">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="7">
         <v>-7.2106548999999998</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="7">
         <v>109.89419669999999</v>
       </c>
       <c r="D18" s="1">
@@ -931,14 +1037,20 @@
       <c r="F18" s="1">
         <v>16</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="4">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="H18" s="18">
+        <v>2002</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
       <c r="D19" s="1">
         <v>2</v>
       </c>
@@ -948,12 +1060,39 @@
       <c r="F19" s="1">
         <v>6</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="4">
         <v>6.3</v>
       </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="34">
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I13"/>
+    <mergeCell ref="I14:I17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="G1:G3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:C19"/>
@@ -963,19 +1102,6 @@
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="G1:G3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
